--- a/Master/3336r00/3336r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/3336r00/3336r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1114,207 +1114,207 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>5.124</v>
+        <v>2.233</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3.774</v>
+        <v>3.6991</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-0.1354</v>
+        <v>-1.4249</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>4.125</v>
+        <v>1.234</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3.8587</v>
+        <v>3.7001</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.281</v>
+        <v>-1.5619</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.0205</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>3.126</v>
+        <v>1.24</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>3.9331</v>
+        <v>3.7393</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>-0.4315</v>
+        <v>-2.3194</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.0176</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>2.127</v>
+        <v>3.238</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4.0017</v>
+        <v>3.7393</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.5869</v>
+        <v>-2.007</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0162</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>1.128</v>
+        <v>2.239</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>4.0616</v>
+        <v>3.7396</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-0.7497</v>
+        <v>-2.1628</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0142</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>6.129</v>
+        <v>5.124</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4.1143</v>
+        <v>3.774</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.6701</v>
+        <v>-0.1354</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0121</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>5.13</v>
+        <v>4.125</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>4.1569</v>
+        <v>3.8587</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-0.8445</v>
+        <v>-0.281</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0091</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>4.131</v>
+        <v>3.126</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>4.1899</v>
+        <v>3.9331</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-1.0228</v>
+        <v>-0.4315</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0072</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>3.132</v>
+        <v>2.127</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>4.2139</v>
+        <v>4.0017</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-1.2065</v>
+        <v>-0.5869</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0043</v>
+        <v>0.0162</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>2.133</v>
+        <v>1.128</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4.227</v>
+        <v>4.0616</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-1.3834</v>
+        <v>-0.7497</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0017</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>6.135</v>
+        <v>6.129</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>6</v>
@@ -1323,33 +1323,133 @@
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
+        <v>4.1143</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>-0.6701</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0.0121</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>4.1569</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>-0.8445</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>4.131</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>4.1899</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>-1.0228</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>4.2139</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>-1.2065</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.0043</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>4.227</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>-1.3834</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>6.135</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="n">
         <v>4.2418</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E49" s="7" t="n">
         <v>-1.478</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F49" s="7" t="n">
         <v>0.0026</v>
       </c>
     </row>
-    <row r="46">
-      <c r="E46" s="8" t="inlineStr">
+    <row r="51">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="E47" s="8" t="inlineStr">
+      <c r="F51" s="9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>1.0491</v>
+      <c r="F52" s="10" t="n">
+        <v>1.0506</v>
       </c>
     </row>
   </sheetData>
